--- a/output/pdf_financials_xlsx/HAI.xlsx
+++ b/output/pdf_financials_xlsx/HAI.xlsx
@@ -2648,10 +2648,10 @@
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>0</v>
+        <v>4.704227</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>0</v>
+        <v>7.952661</v>
       </c>
       <c r="D91" s="1" t="inlineStr">
         <is>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>8.764066</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0</v>
+        <v>11.314091</v>
       </c>
     </row>
     <row r="92">
@@ -4767,7 +4767,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -5700,7 +5704,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E49" s="5" t="n">
         <v>4.704227</v>
       </c>

--- a/output/pdf_financials_xlsx/HAI.xlsx
+++ b/output/pdf_financials_xlsx/HAI.xlsx
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>5.772663</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>8.285686999999999</v>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>16.471364</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>17.198767</v>
       </c>
     </row>
     <row r="35">
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>5.772663</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>8.285686999999999</v>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
@@ -1283,10 +1283,10 @@
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>16.471364</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>17.198767</v>
       </c>
     </row>
     <row r="37">
@@ -1560,10 +1560,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>13.897326</v>
+        <v>8.124663</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>14.566604</v>
+        <v>6.280917</v>
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>22.447799</v>
+        <v>5.976435</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>23.484392</v>
+        <v>6.285625</v>
       </c>
     </row>
     <row r="49">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/HAI.xlsx
+++ b/output/pdf_financials_xlsx/HAI.xlsx
@@ -1083,19 +1083,19 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>1.310594</v>
+        <v>1.834231</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>5.624995</v>
+        <v>6.730646</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>6.750776</v>
+        <v>8.150145999999999</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>6.266746</v>
+        <v>8.049918</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>5.073539</v>
+        <v>7.287131</v>
       </c>
     </row>
     <row r="29">
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>10.965351</v>
+        <v>12.748523</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>5.188176</v>
+        <v>7.401768</v>
       </c>
     </row>
     <row r="30">
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>8.465023799542301</v>
+        <v>9.84159564103442</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>3.769516777565992</v>
+        <v>5.377822313593656</v>
       </c>
     </row>
     <row r="31">
@@ -2875,19 +2875,19 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>1.834231</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>6.730646</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>8.150145999999999</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>8.049918</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>7.287131</v>
       </c>
     </row>
     <row r="101">
@@ -6274,7 +6274,11 @@
           <t>Depreciation of property and equipment 8</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -6354,7 +6358,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6883,7 +6887,11 @@
           <t>Depreciation of property and equipment 9</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E78" s="5" t="n">
         <v>0.523637</v>
       </c>
@@ -6959,7 +6967,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E80" s="5" t="n">

--- a/output/pdf_financials_xlsx/HAI.xlsx
+++ b/output/pdf_financials_xlsx/HAI.xlsx
@@ -4611,7 +4611,11 @@
           <t>Lease liabilities 7</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -5548,7 +5552,11 @@
           <t>Lease liabilities 8</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E45" s="5" t="n">
         <v>8.258073</v>
       </c>
